--- a/testing/vulnerability/vulnerability_report.xlsx
+++ b/testing/vulnerability/vulnerability_report.xlsx
@@ -2107,7 +2107,7 @@
         <v>14</v>
       </c>
       <c r="H2" s="6">
-        <v>84</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2133,7 +2133,7 @@
         <v>14</v>
       </c>
       <c r="H3" s="8">
-        <v>35</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2159,7 +2159,7 @@
         <v>14</v>
       </c>
       <c r="H4" s="6">
-        <v>70</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2185,7 +2185,7 @@
         <v>14</v>
       </c>
       <c r="H5" s="8">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2211,7 +2211,7 @@
         <v>14</v>
       </c>
       <c r="H6" s="6">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2237,7 +2237,7 @@
         <v>14</v>
       </c>
       <c r="H7" s="8">
-        <v>97</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2263,7 +2263,7 @@
         <v>14</v>
       </c>
       <c r="H8" s="6">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2289,7 +2289,7 @@
         <v>14</v>
       </c>
       <c r="H9" s="8">
-        <v>60</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2315,7 +2315,7 @@
         <v>14</v>
       </c>
       <c r="H10" s="6">
-        <v>53</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2341,7 +2341,7 @@
         <v>14</v>
       </c>
       <c r="H11" s="8">
-        <v>80</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2367,7 +2367,7 @@
         <v>14</v>
       </c>
       <c r="H12" s="6">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2393,7 +2393,7 @@
         <v>14</v>
       </c>
       <c r="H13" s="8">
-        <v>80</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2419,7 +2419,7 @@
         <v>14</v>
       </c>
       <c r="H14" s="6">
-        <v>92</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2445,7 +2445,7 @@
         <v>14</v>
       </c>
       <c r="H15" s="8">
-        <v>21</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2471,7 +2471,7 @@
         <v>14</v>
       </c>
       <c r="H16" s="6">
-        <v>49</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2497,7 +2497,7 @@
         <v>14</v>
       </c>
       <c r="H17" s="8">
-        <v>74</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2523,7 +2523,7 @@
         <v>14</v>
       </c>
       <c r="H18" s="6">
-        <v>101</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2549,7 +2549,7 @@
         <v>14</v>
       </c>
       <c r="H19" s="8">
-        <v>27</v>
+        <v>88</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2575,7 +2575,7 @@
         <v>14</v>
       </c>
       <c r="H20" s="6">
-        <v>89</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2601,7 +2601,7 @@
         <v>14</v>
       </c>
       <c r="H21" s="8">
-        <v>99</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2627,7 +2627,7 @@
         <v>14</v>
       </c>
       <c r="H22" s="6">
-        <v>68</v>
+        <v>104</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2653,7 +2653,7 @@
         <v>14</v>
       </c>
       <c r="H23" s="8">
-        <v>30</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2679,7 +2679,7 @@
         <v>14</v>
       </c>
       <c r="H24" s="6">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2705,7 +2705,7 @@
         <v>14</v>
       </c>
       <c r="H25" s="8">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2731,7 +2731,7 @@
         <v>14</v>
       </c>
       <c r="H26" s="6">
-        <v>87</v>
+        <v>102</v>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2757,7 +2757,7 @@
         <v>14</v>
       </c>
       <c r="H27" s="8">
-        <v>43</v>
+        <v>92</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2783,7 +2783,7 @@
         <v>14</v>
       </c>
       <c r="H28" s="6">
-        <v>29</v>
+        <v>40</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2809,7 +2809,7 @@
         <v>14</v>
       </c>
       <c r="H29" s="8">
-        <v>65</v>
+        <v>18</v>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2835,7 +2835,7 @@
         <v>14</v>
       </c>
       <c r="H30" s="6">
-        <v>51</v>
+        <v>73</v>
       </c>
     </row>
     <row r="31" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2861,7 +2861,7 @@
         <v>14</v>
       </c>
       <c r="H31" s="8">
-        <v>65</v>
+        <v>56</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2887,7 +2887,7 @@
         <v>14</v>
       </c>
       <c r="H32" s="6">
-        <v>20</v>
+        <v>74</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2913,7 +2913,7 @@
         <v>14</v>
       </c>
       <c r="H33" s="8">
-        <v>32</v>
+        <v>83</v>
       </c>
     </row>
     <row r="34" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2939,7 +2939,7 @@
         <v>14</v>
       </c>
       <c r="H34" s="6">
-        <v>32</v>
+        <v>50</v>
       </c>
     </row>
     <row r="35" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2965,7 +2965,7 @@
         <v>14</v>
       </c>
       <c r="H35" s="8">
-        <v>102</v>
+        <v>45</v>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2991,7 +2991,7 @@
         <v>14</v>
       </c>
       <c r="H36" s="6">
-        <v>27</v>
+        <v>90</v>
       </c>
     </row>
     <row r="37" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3017,7 +3017,7 @@
         <v>14</v>
       </c>
       <c r="H37" s="8">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
     <row r="38" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3043,7 +3043,7 @@
         <v>14</v>
       </c>
       <c r="H38" s="6">
-        <v>89</v>
+        <v>76</v>
       </c>
     </row>
     <row r="39" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3069,7 +3069,7 @@
         <v>14</v>
       </c>
       <c r="H39" s="8">
-        <v>85</v>
+        <v>75</v>
       </c>
     </row>
     <row r="40" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3095,7 +3095,7 @@
         <v>14</v>
       </c>
       <c r="H40" s="6">
-        <v>47</v>
+        <v>86</v>
       </c>
     </row>
     <row r="41" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3121,7 +3121,7 @@
         <v>14</v>
       </c>
       <c r="H41" s="8">
-        <v>103</v>
+        <v>37</v>
       </c>
     </row>
     <row r="42" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3147,7 +3147,7 @@
         <v>14</v>
       </c>
       <c r="H42" s="6">
-        <v>74</v>
+        <v>59</v>
       </c>
     </row>
     <row r="43" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3173,7 +3173,7 @@
         <v>14</v>
       </c>
       <c r="H43" s="8">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="44" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3199,7 +3199,7 @@
         <v>14</v>
       </c>
       <c r="H44" s="6">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="45" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3225,7 +3225,7 @@
         <v>14</v>
       </c>
       <c r="H45" s="8">
-        <v>77</v>
+        <v>25</v>
       </c>
     </row>
     <row r="46" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3251,7 +3251,7 @@
         <v>14</v>
       </c>
       <c r="H46" s="6">
-        <v>82</v>
+        <v>19</v>
       </c>
     </row>
     <row r="47" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3277,7 +3277,7 @@
         <v>14</v>
       </c>
       <c r="H47" s="8">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="48" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3303,7 +3303,7 @@
         <v>14</v>
       </c>
       <c r="H48" s="6">
-        <v>15</v>
+        <v>61</v>
       </c>
     </row>
     <row r="49" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3329,7 +3329,7 @@
         <v>14</v>
       </c>
       <c r="H49" s="8">
-        <v>68</v>
+        <v>16</v>
       </c>
     </row>
     <row r="50" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3355,7 +3355,7 @@
         <v>14</v>
       </c>
       <c r="H50" s="6">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="51" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3381,7 +3381,7 @@
         <v>14</v>
       </c>
       <c r="H51" s="8">
-        <v>98</v>
+        <v>52</v>
       </c>
     </row>
     <row r="52" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3407,7 +3407,7 @@
         <v>14</v>
       </c>
       <c r="H52" s="6">
-        <v>99</v>
+        <v>46</v>
       </c>
     </row>
     <row r="53" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3433,7 +3433,7 @@
         <v>14</v>
       </c>
       <c r="H53" s="8">
-        <v>27</v>
+        <v>86</v>
       </c>
     </row>
     <row r="54" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3459,7 +3459,7 @@
         <v>14</v>
       </c>
       <c r="H54" s="6">
-        <v>31</v>
+        <v>18</v>
       </c>
     </row>
     <row r="55" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3485,7 +3485,7 @@
         <v>14</v>
       </c>
       <c r="H55" s="8">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="56" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3511,7 +3511,7 @@
         <v>14</v>
       </c>
       <c r="H56" s="6">
-        <v>52</v>
+        <v>64</v>
       </c>
     </row>
     <row r="57" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3537,7 +3537,7 @@
         <v>14</v>
       </c>
       <c r="H57" s="8">
-        <v>97</v>
+        <v>23</v>
       </c>
     </row>
     <row r="58" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3563,7 +3563,7 @@
         <v>14</v>
       </c>
       <c r="H58" s="6">
-        <v>42</v>
+        <v>57</v>
       </c>
     </row>
     <row r="59" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3589,7 +3589,7 @@
         <v>14</v>
       </c>
       <c r="H59" s="8">
-        <v>30</v>
+        <v>101</v>
       </c>
     </row>
     <row r="60" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3615,7 +3615,7 @@
         <v>14</v>
       </c>
       <c r="H60" s="6">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="61" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3641,7 +3641,7 @@
         <v>14</v>
       </c>
       <c r="H61" s="8">
-        <v>22</v>
+        <v>102</v>
       </c>
     </row>
     <row r="62" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3667,7 +3667,7 @@
         <v>14</v>
       </c>
       <c r="H62" s="6">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="63" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3693,7 +3693,7 @@
         <v>14</v>
       </c>
       <c r="H63" s="8">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="64" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3719,7 +3719,7 @@
         <v>14</v>
       </c>
       <c r="H64" s="6">
-        <v>15</v>
+        <v>54</v>
       </c>
     </row>
     <row r="65" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3745,7 +3745,7 @@
         <v>14</v>
       </c>
       <c r="H65" s="8">
-        <v>51</v>
+        <v>59</v>
       </c>
     </row>
     <row r="66" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3771,7 +3771,7 @@
         <v>14</v>
       </c>
       <c r="H66" s="6">
-        <v>79</v>
+        <v>103</v>
       </c>
     </row>
     <row r="67" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3797,7 +3797,7 @@
         <v>14</v>
       </c>
       <c r="H67" s="8">
-        <v>31</v>
+        <v>61</v>
       </c>
     </row>
     <row r="68" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3823,7 +3823,7 @@
         <v>14</v>
       </c>
       <c r="H68" s="6">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="69" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3849,7 +3849,7 @@
         <v>14</v>
       </c>
       <c r="H69" s="8">
-        <v>55</v>
+        <v>100</v>
       </c>
     </row>
     <row r="70" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3875,7 +3875,7 @@
         <v>14</v>
       </c>
       <c r="H70" s="6">
-        <v>35</v>
+        <v>75</v>
       </c>
     </row>
     <row r="71" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3901,7 +3901,7 @@
         <v>14</v>
       </c>
       <c r="H71" s="8">
-        <v>25</v>
+        <v>99</v>
       </c>
     </row>
     <row r="72" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3927,7 +3927,7 @@
         <v>14</v>
       </c>
       <c r="H72" s="6">
-        <v>21</v>
+        <v>100</v>
       </c>
     </row>
     <row r="73" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3953,7 +3953,7 @@
         <v>14</v>
       </c>
       <c r="H73" s="8">
-        <v>61</v>
+        <v>51</v>
       </c>
     </row>
     <row r="74" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3979,7 +3979,7 @@
         <v>14</v>
       </c>
       <c r="H74" s="6">
-        <v>67</v>
+        <v>78</v>
       </c>
     </row>
     <row r="75" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4005,7 +4005,7 @@
         <v>14</v>
       </c>
       <c r="H75" s="8">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="76" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4031,7 +4031,7 @@
         <v>14</v>
       </c>
       <c r="H76" s="6">
-        <v>57</v>
+        <v>42</v>
       </c>
     </row>
     <row r="77" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4057,7 +4057,7 @@
         <v>14</v>
       </c>
       <c r="H77" s="8">
-        <v>36</v>
+        <v>48</v>
       </c>
     </row>
     <row r="78" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4083,7 +4083,7 @@
         <v>14</v>
       </c>
       <c r="H78" s="6">
-        <v>42</v>
+        <v>32</v>
       </c>
     </row>
     <row r="79" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4109,7 +4109,7 @@
         <v>14</v>
       </c>
       <c r="H79" s="8">
-        <v>24</v>
+        <v>96</v>
       </c>
     </row>
     <row r="80" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4135,7 +4135,7 @@
         <v>14</v>
       </c>
       <c r="H80" s="6">
-        <v>82</v>
+        <v>73</v>
       </c>
     </row>
     <row r="81" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4161,7 +4161,7 @@
         <v>14</v>
       </c>
       <c r="H81" s="8">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="82" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4187,7 +4187,7 @@
         <v>14</v>
       </c>
       <c r="H82" s="6">
-        <v>102</v>
+        <v>51</v>
       </c>
     </row>
     <row r="83" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4213,7 +4213,7 @@
         <v>14</v>
       </c>
       <c r="H83" s="8">
-        <v>57</v>
+        <v>46</v>
       </c>
     </row>
     <row r="84" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4239,7 +4239,7 @@
         <v>14</v>
       </c>
       <c r="H84" s="6">
-        <v>29</v>
+        <v>84</v>
       </c>
     </row>
     <row r="85" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4265,7 +4265,7 @@
         <v>14</v>
       </c>
       <c r="H85" s="8">
-        <v>26</v>
+        <v>78</v>
       </c>
     </row>
     <row r="86" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4291,7 +4291,7 @@
         <v>14</v>
       </c>
       <c r="H86" s="6">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="87" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4317,7 +4317,7 @@
         <v>14</v>
       </c>
       <c r="H87" s="8">
-        <v>82</v>
+        <v>92</v>
       </c>
     </row>
     <row r="88" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4343,7 +4343,7 @@
         <v>14</v>
       </c>
       <c r="H88" s="6">
-        <v>35</v>
+        <v>57</v>
       </c>
     </row>
     <row r="89" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4369,7 +4369,7 @@
         <v>14</v>
       </c>
       <c r="H89" s="8">
-        <v>67</v>
+        <v>74</v>
       </c>
     </row>
     <row r="90" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4395,7 +4395,7 @@
         <v>14</v>
       </c>
       <c r="H90" s="6">
-        <v>101</v>
+        <v>35</v>
       </c>
     </row>
     <row r="91" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4421,7 +4421,7 @@
         <v>14</v>
       </c>
       <c r="H91" s="8">
-        <v>77</v>
+        <v>46</v>
       </c>
     </row>
     <row r="92" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4447,7 +4447,7 @@
         <v>14</v>
       </c>
       <c r="H92" s="6">
-        <v>55</v>
+        <v>79</v>
       </c>
     </row>
     <row r="93" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4473,7 +4473,7 @@
         <v>14</v>
       </c>
       <c r="H93" s="8">
-        <v>18</v>
+        <v>42</v>
       </c>
     </row>
     <row r="94" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4499,7 +4499,7 @@
         <v>14</v>
       </c>
       <c r="H94" s="6">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="95" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4525,7 +4525,7 @@
         <v>14</v>
       </c>
       <c r="H95" s="8">
-        <v>93</v>
+        <v>48</v>
       </c>
     </row>
     <row r="96" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4551,7 +4551,7 @@
         <v>14</v>
       </c>
       <c r="H96" s="6">
-        <v>82</v>
+        <v>60</v>
       </c>
     </row>
     <row r="97" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4577,7 +4577,7 @@
         <v>14</v>
       </c>
       <c r="H97" s="8">
-        <v>96</v>
+        <v>103</v>
       </c>
     </row>
     <row r="98" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4603,7 +4603,7 @@
         <v>14</v>
       </c>
       <c r="H98" s="6">
-        <v>65</v>
+        <v>53</v>
       </c>
     </row>
     <row r="99" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4629,7 +4629,7 @@
         <v>14</v>
       </c>
       <c r="H99" s="8">
-        <v>52</v>
+        <v>38</v>
       </c>
     </row>
     <row r="100" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4655,7 +4655,7 @@
         <v>14</v>
       </c>
       <c r="H100" s="6">
-        <v>42</v>
+        <v>98</v>
       </c>
     </row>
     <row r="101" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4707,7 +4707,7 @@
         <v>14</v>
       </c>
       <c r="H102" s="6">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="103" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4733,7 +4733,7 @@
         <v>14</v>
       </c>
       <c r="H103" s="8">
-        <v>95</v>
+        <v>76</v>
       </c>
     </row>
     <row r="104" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4785,7 +4785,7 @@
         <v>14</v>
       </c>
       <c r="H105" s="8">
-        <v>99</v>
+        <v>20</v>
       </c>
     </row>
     <row r="106" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4811,7 +4811,7 @@
         <v>14</v>
       </c>
       <c r="H106" s="6">
-        <v>17</v>
+        <v>70</v>
       </c>
     </row>
     <row r="107" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4837,7 +4837,7 @@
         <v>14</v>
       </c>
       <c r="H107" s="8">
-        <v>48</v>
+        <v>19</v>
       </c>
     </row>
     <row r="108" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4863,7 +4863,7 @@
         <v>14</v>
       </c>
       <c r="H108" s="6">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="109" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4889,7 +4889,7 @@
         <v>14</v>
       </c>
       <c r="H109" s="8">
-        <v>47</v>
+        <v>54</v>
       </c>
     </row>
     <row r="110" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4915,7 +4915,7 @@
         <v>14</v>
       </c>
       <c r="H110" s="6">
-        <v>104</v>
+        <v>41</v>
       </c>
     </row>
     <row r="111" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4941,7 +4941,7 @@
         <v>14</v>
       </c>
       <c r="H111" s="8">
-        <v>72</v>
+        <v>63</v>
       </c>
     </row>
     <row r="112" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4967,7 +4967,7 @@
         <v>14</v>
       </c>
       <c r="H112" s="6">
-        <v>35</v>
+        <v>80</v>
       </c>
     </row>
     <row r="113" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4993,7 +4993,7 @@
         <v>14</v>
       </c>
       <c r="H113" s="8">
-        <v>57</v>
+        <v>34</v>
       </c>
     </row>
     <row r="114" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5019,7 +5019,7 @@
         <v>14</v>
       </c>
       <c r="H114" s="6">
-        <v>77</v>
+        <v>20</v>
       </c>
     </row>
     <row r="115" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5045,7 +5045,7 @@
         <v>14</v>
       </c>
       <c r="H115" s="8">
-        <v>79</v>
+        <v>86</v>
       </c>
     </row>
     <row r="116" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5071,7 +5071,7 @@
         <v>14</v>
       </c>
       <c r="H116" s="6">
-        <v>84</v>
+        <v>36</v>
       </c>
     </row>
     <row r="117" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5097,7 +5097,7 @@
         <v>14</v>
       </c>
       <c r="H117" s="8">
-        <v>68</v>
+        <v>104</v>
       </c>
     </row>
     <row r="118" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5123,7 +5123,7 @@
         <v>14</v>
       </c>
       <c r="H118" s="6">
-        <v>77</v>
+        <v>32</v>
       </c>
     </row>
     <row r="119" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5149,7 +5149,7 @@
         <v>14</v>
       </c>
       <c r="H119" s="8">
-        <v>46</v>
+        <v>52</v>
       </c>
     </row>
     <row r="120" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5175,7 +5175,7 @@
         <v>14</v>
       </c>
       <c r="H120" s="6">
-        <v>53</v>
+        <v>42</v>
       </c>
     </row>
     <row r="121" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5201,7 +5201,7 @@
         <v>14</v>
       </c>
       <c r="H121" s="8">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="122" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5227,7 +5227,7 @@
         <v>14</v>
       </c>
       <c r="H122" s="6">
-        <v>64</v>
+        <v>41</v>
       </c>
     </row>
     <row r="123" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5253,7 +5253,7 @@
         <v>14</v>
       </c>
       <c r="H123" s="8">
-        <v>104</v>
+        <v>72</v>
       </c>
     </row>
     <row r="124" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5279,7 +5279,7 @@
         <v>14</v>
       </c>
       <c r="H124" s="6">
-        <v>82</v>
+        <v>50</v>
       </c>
     </row>
     <row r="125" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5305,7 +5305,7 @@
         <v>14</v>
       </c>
       <c r="H125" s="8">
-        <v>21</v>
+        <v>85</v>
       </c>
     </row>
     <row r="126" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5331,7 +5331,7 @@
         <v>14</v>
       </c>
       <c r="H126" s="6">
-        <v>65</v>
+        <v>40</v>
       </c>
     </row>
     <row r="127" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5357,7 +5357,7 @@
         <v>14</v>
       </c>
       <c r="H127" s="8">
-        <v>33</v>
+        <v>72</v>
       </c>
     </row>
     <row r="128" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5383,7 +5383,7 @@
         <v>14</v>
       </c>
       <c r="H128" s="6">
-        <v>77</v>
+        <v>91</v>
       </c>
     </row>
     <row r="129" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5409,7 +5409,7 @@
         <v>14</v>
       </c>
       <c r="H129" s="8">
-        <v>37</v>
+        <v>71</v>
       </c>
     </row>
     <row r="130" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5435,7 +5435,7 @@
         <v>14</v>
       </c>
       <c r="H130" s="6">
-        <v>36</v>
+        <v>102</v>
       </c>
     </row>
     <row r="131" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5461,7 +5461,7 @@
         <v>14</v>
       </c>
       <c r="H131" s="8">
-        <v>21</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/testing/vulnerability/vulnerability_report.xlsx
+++ b/testing/vulnerability/vulnerability_report.xlsx
@@ -2133,7 +2133,7 @@
         <v>14</v>
       </c>
       <c r="H3" s="8">
-        <v>103</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2159,7 +2159,7 @@
         <v>14</v>
       </c>
       <c r="H4" s="6">
-        <v>104</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2185,7 +2185,7 @@
         <v>14</v>
       </c>
       <c r="H5" s="8">
-        <v>71</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2211,7 +2211,7 @@
         <v>14</v>
       </c>
       <c r="H6" s="6">
-        <v>18</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2237,7 +2237,7 @@
         <v>14</v>
       </c>
       <c r="H7" s="8">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2263,7 +2263,7 @@
         <v>14</v>
       </c>
       <c r="H8" s="6">
-        <v>38</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2289,7 +2289,7 @@
         <v>14</v>
       </c>
       <c r="H9" s="8">
-        <v>73</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2315,7 +2315,7 @@
         <v>14</v>
       </c>
       <c r="H10" s="6">
-        <v>62</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2341,7 +2341,7 @@
         <v>14</v>
       </c>
       <c r="H11" s="8">
-        <v>63</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2367,7 +2367,7 @@
         <v>14</v>
       </c>
       <c r="H12" s="6">
-        <v>54</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2393,7 +2393,7 @@
         <v>14</v>
       </c>
       <c r="H13" s="8">
-        <v>24</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2419,7 +2419,7 @@
         <v>14</v>
       </c>
       <c r="H14" s="6">
-        <v>19</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2445,7 +2445,7 @@
         <v>14</v>
       </c>
       <c r="H15" s="8">
-        <v>35</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2471,7 +2471,7 @@
         <v>14</v>
       </c>
       <c r="H16" s="6">
-        <v>82</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2497,7 +2497,7 @@
         <v>14</v>
       </c>
       <c r="H17" s="8">
-        <v>19</v>
+        <v>94</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2523,7 +2523,7 @@
         <v>14</v>
       </c>
       <c r="H18" s="6">
-        <v>58</v>
+        <v>71</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2549,7 +2549,7 @@
         <v>14</v>
       </c>
       <c r="H19" s="8">
-        <v>88</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2575,7 +2575,7 @@
         <v>14</v>
       </c>
       <c r="H20" s="6">
-        <v>17</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2601,7 +2601,7 @@
         <v>14</v>
       </c>
       <c r="H21" s="8">
-        <v>62</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2627,7 +2627,7 @@
         <v>14</v>
       </c>
       <c r="H22" s="6">
-        <v>104</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2653,7 +2653,7 @@
         <v>14</v>
       </c>
       <c r="H23" s="8">
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2679,7 +2679,7 @@
         <v>14</v>
       </c>
       <c r="H24" s="6">
-        <v>30</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2705,7 +2705,7 @@
         <v>14</v>
       </c>
       <c r="H25" s="8">
-        <v>87</v>
+        <v>65</v>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2731,7 +2731,7 @@
         <v>14</v>
       </c>
       <c r="H26" s="6">
-        <v>102</v>
+        <v>91</v>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2757,7 +2757,7 @@
         <v>14</v>
       </c>
       <c r="H27" s="8">
-        <v>92</v>
+        <v>50</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2783,7 +2783,7 @@
         <v>14</v>
       </c>
       <c r="H28" s="6">
-        <v>40</v>
+        <v>74</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2809,7 +2809,7 @@
         <v>14</v>
       </c>
       <c r="H29" s="8">
-        <v>18</v>
+        <v>32</v>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2835,7 +2835,7 @@
         <v>14</v>
       </c>
       <c r="H30" s="6">
-        <v>73</v>
+        <v>40</v>
       </c>
     </row>
     <row r="31" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2861,7 +2861,7 @@
         <v>14</v>
       </c>
       <c r="H31" s="8">
-        <v>56</v>
+        <v>63</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2887,7 +2887,7 @@
         <v>14</v>
       </c>
       <c r="H32" s="6">
-        <v>74</v>
+        <v>31</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2913,7 +2913,7 @@
         <v>14</v>
       </c>
       <c r="H33" s="8">
-        <v>83</v>
+        <v>15</v>
       </c>
     </row>
     <row r="34" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2939,7 +2939,7 @@
         <v>14</v>
       </c>
       <c r="H34" s="6">
-        <v>50</v>
+        <v>17</v>
       </c>
     </row>
     <row r="35" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2965,7 +2965,7 @@
         <v>14</v>
       </c>
       <c r="H35" s="8">
-        <v>45</v>
+        <v>54</v>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -2991,7 +2991,7 @@
         <v>14</v>
       </c>
       <c r="H36" s="6">
-        <v>90</v>
+        <v>68</v>
       </c>
     </row>
     <row r="37" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3017,7 +3017,7 @@
         <v>14</v>
       </c>
       <c r="H37" s="8">
-        <v>86</v>
+        <v>45</v>
       </c>
     </row>
     <row r="38" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3043,7 +3043,7 @@
         <v>14</v>
       </c>
       <c r="H38" s="6">
-        <v>76</v>
+        <v>56</v>
       </c>
     </row>
     <row r="39" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3069,7 +3069,7 @@
         <v>14</v>
       </c>
       <c r="H39" s="8">
-        <v>75</v>
+        <v>66</v>
       </c>
     </row>
     <row r="40" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3095,7 +3095,7 @@
         <v>14</v>
       </c>
       <c r="H40" s="6">
-        <v>86</v>
+        <v>101</v>
       </c>
     </row>
     <row r="41" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3121,7 +3121,7 @@
         <v>14</v>
       </c>
       <c r="H41" s="8">
-        <v>37</v>
+        <v>75</v>
       </c>
     </row>
     <row r="42" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3173,7 +3173,7 @@
         <v>14</v>
       </c>
       <c r="H43" s="8">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="44" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3199,7 +3199,7 @@
         <v>14</v>
       </c>
       <c r="H44" s="6">
-        <v>67</v>
+        <v>39</v>
       </c>
     </row>
     <row r="45" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3225,7 +3225,7 @@
         <v>14</v>
       </c>
       <c r="H45" s="8">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="46" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3251,7 +3251,7 @@
         <v>14</v>
       </c>
       <c r="H46" s="6">
-        <v>19</v>
+        <v>98</v>
       </c>
     </row>
     <row r="47" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3277,7 +3277,7 @@
         <v>14</v>
       </c>
       <c r="H47" s="8">
-        <v>20</v>
+        <v>82</v>
       </c>
     </row>
     <row r="48" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3303,7 +3303,7 @@
         <v>14</v>
       </c>
       <c r="H48" s="6">
-        <v>61</v>
+        <v>42</v>
       </c>
     </row>
     <row r="49" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3329,7 +3329,7 @@
         <v>14</v>
       </c>
       <c r="H49" s="8">
-        <v>16</v>
+        <v>92</v>
       </c>
     </row>
     <row r="50" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3355,7 +3355,7 @@
         <v>14</v>
       </c>
       <c r="H50" s="6">
-        <v>95</v>
+        <v>32</v>
       </c>
     </row>
     <row r="51" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3381,7 +3381,7 @@
         <v>14</v>
       </c>
       <c r="H51" s="8">
-        <v>52</v>
+        <v>67</v>
       </c>
     </row>
     <row r="52" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3407,7 +3407,7 @@
         <v>14</v>
       </c>
       <c r="H52" s="6">
-        <v>46</v>
+        <v>28</v>
       </c>
     </row>
     <row r="53" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3433,7 +3433,7 @@
         <v>14</v>
       </c>
       <c r="H53" s="8">
-        <v>86</v>
+        <v>18</v>
       </c>
     </row>
     <row r="54" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3459,7 +3459,7 @@
         <v>14</v>
       </c>
       <c r="H54" s="6">
-        <v>18</v>
+        <v>28</v>
       </c>
     </row>
     <row r="55" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3485,7 +3485,7 @@
         <v>14</v>
       </c>
       <c r="H55" s="8">
-        <v>31</v>
+        <v>42</v>
       </c>
     </row>
     <row r="56" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3511,7 +3511,7 @@
         <v>14</v>
       </c>
       <c r="H56" s="6">
-        <v>64</v>
+        <v>101</v>
       </c>
     </row>
     <row r="57" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3537,7 +3537,7 @@
         <v>14</v>
       </c>
       <c r="H57" s="8">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="58" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3563,7 +3563,7 @@
         <v>14</v>
       </c>
       <c r="H58" s="6">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="59" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3589,7 +3589,7 @@
         <v>14</v>
       </c>
       <c r="H59" s="8">
-        <v>101</v>
+        <v>76</v>
       </c>
     </row>
     <row r="60" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3615,7 +3615,7 @@
         <v>14</v>
       </c>
       <c r="H60" s="6">
-        <v>41</v>
+        <v>99</v>
       </c>
     </row>
     <row r="61" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3641,7 +3641,7 @@
         <v>14</v>
       </c>
       <c r="H61" s="8">
-        <v>102</v>
+        <v>33</v>
       </c>
     </row>
     <row r="62" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3693,7 +3693,7 @@
         <v>14</v>
       </c>
       <c r="H63" s="8">
-        <v>29</v>
+        <v>90</v>
       </c>
     </row>
     <row r="64" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3719,7 +3719,7 @@
         <v>14</v>
       </c>
       <c r="H64" s="6">
-        <v>54</v>
+        <v>89</v>
       </c>
     </row>
     <row r="65" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3745,7 +3745,7 @@
         <v>14</v>
       </c>
       <c r="H65" s="8">
-        <v>59</v>
+        <v>71</v>
       </c>
     </row>
     <row r="66" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3771,7 +3771,7 @@
         <v>14</v>
       </c>
       <c r="H66" s="6">
-        <v>103</v>
+        <v>41</v>
       </c>
     </row>
     <row r="67" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3797,7 +3797,7 @@
         <v>14</v>
       </c>
       <c r="H67" s="8">
-        <v>61</v>
+        <v>95</v>
       </c>
     </row>
     <row r="68" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3823,7 +3823,7 @@
         <v>14</v>
       </c>
       <c r="H68" s="6">
-        <v>49</v>
+        <v>17</v>
       </c>
     </row>
     <row r="69" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3849,7 +3849,7 @@
         <v>14</v>
       </c>
       <c r="H69" s="8">
-        <v>100</v>
+        <v>65</v>
       </c>
     </row>
     <row r="70" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3875,7 +3875,7 @@
         <v>14</v>
       </c>
       <c r="H70" s="6">
-        <v>75</v>
+        <v>102</v>
       </c>
     </row>
     <row r="71" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3901,7 +3901,7 @@
         <v>14</v>
       </c>
       <c r="H71" s="8">
-        <v>99</v>
+        <v>41</v>
       </c>
     </row>
     <row r="72" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3927,7 +3927,7 @@
         <v>14</v>
       </c>
       <c r="H72" s="6">
-        <v>100</v>
+        <v>15</v>
       </c>
     </row>
     <row r="73" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3953,7 +3953,7 @@
         <v>14</v>
       </c>
       <c r="H73" s="8">
-        <v>51</v>
+        <v>103</v>
       </c>
     </row>
     <row r="74" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -3979,7 +3979,7 @@
         <v>14</v>
       </c>
       <c r="H74" s="6">
-        <v>78</v>
+        <v>40</v>
       </c>
     </row>
     <row r="75" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4005,7 +4005,7 @@
         <v>14</v>
       </c>
       <c r="H75" s="8">
-        <v>89</v>
+        <v>50</v>
       </c>
     </row>
     <row r="76" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4031,7 +4031,7 @@
         <v>14</v>
       </c>
       <c r="H76" s="6">
-        <v>42</v>
+        <v>71</v>
       </c>
     </row>
     <row r="77" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4057,7 +4057,7 @@
         <v>14</v>
       </c>
       <c r="H77" s="8">
-        <v>48</v>
+        <v>95</v>
       </c>
     </row>
     <row r="78" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4083,7 +4083,7 @@
         <v>14</v>
       </c>
       <c r="H78" s="6">
-        <v>32</v>
+        <v>97</v>
       </c>
     </row>
     <row r="79" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4109,7 +4109,7 @@
         <v>14</v>
       </c>
       <c r="H79" s="8">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="80" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4135,7 +4135,7 @@
         <v>14</v>
       </c>
       <c r="H80" s="6">
-        <v>73</v>
+        <v>56</v>
       </c>
     </row>
     <row r="81" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4161,7 +4161,7 @@
         <v>14</v>
       </c>
       <c r="H81" s="8">
-        <v>48</v>
+        <v>101</v>
       </c>
     </row>
     <row r="82" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4187,7 +4187,7 @@
         <v>14</v>
       </c>
       <c r="H82" s="6">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="83" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4213,7 +4213,7 @@
         <v>14</v>
       </c>
       <c r="H83" s="8">
-        <v>46</v>
+        <v>79</v>
       </c>
     </row>
     <row r="84" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4239,7 +4239,7 @@
         <v>14</v>
       </c>
       <c r="H84" s="6">
-        <v>84</v>
+        <v>50</v>
       </c>
     </row>
     <row r="85" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4265,7 +4265,7 @@
         <v>14</v>
       </c>
       <c r="H85" s="8">
-        <v>78</v>
+        <v>39</v>
       </c>
     </row>
     <row r="86" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4291,7 +4291,7 @@
         <v>14</v>
       </c>
       <c r="H86" s="6">
-        <v>51</v>
+        <v>102</v>
       </c>
     </row>
     <row r="87" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4317,7 +4317,7 @@
         <v>14</v>
       </c>
       <c r="H87" s="8">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="88" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4343,7 +4343,7 @@
         <v>14</v>
       </c>
       <c r="H88" s="6">
-        <v>57</v>
+        <v>50</v>
       </c>
     </row>
     <row r="89" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4369,7 +4369,7 @@
         <v>14</v>
       </c>
       <c r="H89" s="8">
-        <v>74</v>
+        <v>82</v>
       </c>
     </row>
     <row r="90" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4395,7 +4395,7 @@
         <v>14</v>
       </c>
       <c r="H90" s="6">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="91" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4421,7 +4421,7 @@
         <v>14</v>
       </c>
       <c r="H91" s="8">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="92" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4447,7 +4447,7 @@
         <v>14</v>
       </c>
       <c r="H92" s="6">
-        <v>79</v>
+        <v>29</v>
       </c>
     </row>
     <row r="93" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4473,7 +4473,7 @@
         <v>14</v>
       </c>
       <c r="H93" s="8">
-        <v>42</v>
+        <v>25</v>
       </c>
     </row>
     <row r="94" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4499,7 +4499,7 @@
         <v>14</v>
       </c>
       <c r="H94" s="6">
-        <v>19</v>
+        <v>73</v>
       </c>
     </row>
     <row r="95" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4525,7 +4525,7 @@
         <v>14</v>
       </c>
       <c r="H95" s="8">
-        <v>48</v>
+        <v>34</v>
       </c>
     </row>
     <row r="96" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4551,7 +4551,7 @@
         <v>14</v>
       </c>
       <c r="H96" s="6">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="97" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4577,7 +4577,7 @@
         <v>14</v>
       </c>
       <c r="H97" s="8">
-        <v>103</v>
+        <v>62</v>
       </c>
     </row>
     <row r="98" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4603,7 +4603,7 @@
         <v>14</v>
       </c>
       <c r="H98" s="6">
-        <v>53</v>
+        <v>103</v>
       </c>
     </row>
     <row r="99" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4629,7 +4629,7 @@
         <v>14</v>
       </c>
       <c r="H99" s="8">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="100" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4655,7 +4655,7 @@
         <v>14</v>
       </c>
       <c r="H100" s="6">
-        <v>98</v>
+        <v>49</v>
       </c>
     </row>
     <row r="101" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4681,7 +4681,7 @@
         <v>14</v>
       </c>
       <c r="H101" s="8">
-        <v>32</v>
+        <v>51</v>
       </c>
     </row>
     <row r="102" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4707,7 +4707,7 @@
         <v>14</v>
       </c>
       <c r="H102" s="6">
-        <v>35</v>
+        <v>98</v>
       </c>
     </row>
     <row r="103" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4733,7 +4733,7 @@
         <v>14</v>
       </c>
       <c r="H103" s="8">
-        <v>76</v>
+        <v>97</v>
       </c>
     </row>
     <row r="104" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4759,7 +4759,7 @@
         <v>14</v>
       </c>
       <c r="H104" s="6">
-        <v>75</v>
+        <v>93</v>
       </c>
     </row>
     <row r="105" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4785,7 +4785,7 @@
         <v>14</v>
       </c>
       <c r="H105" s="8">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="106" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4837,7 +4837,7 @@
         <v>14</v>
       </c>
       <c r="H107" s="8">
-        <v>19</v>
+        <v>102</v>
       </c>
     </row>
     <row r="108" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4863,7 +4863,7 @@
         <v>14</v>
       </c>
       <c r="H108" s="6">
-        <v>38</v>
+        <v>48</v>
       </c>
     </row>
     <row r="109" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4889,7 +4889,7 @@
         <v>14</v>
       </c>
       <c r="H109" s="8">
-        <v>54</v>
+        <v>67</v>
       </c>
     </row>
     <row r="110" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4915,7 +4915,7 @@
         <v>14</v>
       </c>
       <c r="H110" s="6">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="111" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4941,7 +4941,7 @@
         <v>14</v>
       </c>
       <c r="H111" s="8">
-        <v>63</v>
+        <v>31</v>
       </c>
     </row>
     <row r="112" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4967,7 +4967,7 @@
         <v>14</v>
       </c>
       <c r="H112" s="6">
-        <v>80</v>
+        <v>99</v>
       </c>
     </row>
     <row r="113" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -4993,7 +4993,7 @@
         <v>14</v>
       </c>
       <c r="H113" s="8">
-        <v>34</v>
+        <v>91</v>
       </c>
     </row>
     <row r="114" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5019,7 +5019,7 @@
         <v>14</v>
       </c>
       <c r="H114" s="6">
-        <v>20</v>
+        <v>72</v>
       </c>
     </row>
     <row r="115" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5045,7 +5045,7 @@
         <v>14</v>
       </c>
       <c r="H115" s="8">
-        <v>86</v>
+        <v>75</v>
       </c>
     </row>
     <row r="116" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5071,7 +5071,7 @@
         <v>14</v>
       </c>
       <c r="H116" s="6">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="117" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5097,7 +5097,7 @@
         <v>14</v>
       </c>
       <c r="H117" s="8">
-        <v>104</v>
+        <v>34</v>
       </c>
     </row>
     <row r="118" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5123,7 +5123,7 @@
         <v>14</v>
       </c>
       <c r="H118" s="6">
-        <v>32</v>
+        <v>76</v>
       </c>
     </row>
     <row r="119" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5149,7 +5149,7 @@
         <v>14</v>
       </c>
       <c r="H119" s="8">
-        <v>52</v>
+        <v>85</v>
       </c>
     </row>
     <row r="120" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5175,7 +5175,7 @@
         <v>14</v>
       </c>
       <c r="H120" s="6">
-        <v>42</v>
+        <v>60</v>
       </c>
     </row>
     <row r="121" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5201,7 +5201,7 @@
         <v>14</v>
       </c>
       <c r="H121" s="8">
-        <v>33</v>
+        <v>71</v>
       </c>
     </row>
     <row r="122" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5227,7 +5227,7 @@
         <v>14</v>
       </c>
       <c r="H122" s="6">
-        <v>41</v>
+        <v>81</v>
       </c>
     </row>
     <row r="123" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5253,7 +5253,7 @@
         <v>14</v>
       </c>
       <c r="H123" s="8">
-        <v>72</v>
+        <v>54</v>
       </c>
     </row>
     <row r="124" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5279,7 +5279,7 @@
         <v>14</v>
       </c>
       <c r="H124" s="6">
-        <v>50</v>
+        <v>92</v>
       </c>
     </row>
     <row r="125" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5305,7 +5305,7 @@
         <v>14</v>
       </c>
       <c r="H125" s="8">
-        <v>85</v>
+        <v>103</v>
       </c>
     </row>
     <row r="126" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5331,7 +5331,7 @@
         <v>14</v>
       </c>
       <c r="H126" s="6">
-        <v>40</v>
+        <v>77</v>
       </c>
     </row>
     <row r="127" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5357,7 +5357,7 @@
         <v>14</v>
       </c>
       <c r="H127" s="8">
-        <v>72</v>
+        <v>45</v>
       </c>
     </row>
     <row r="128" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5383,7 +5383,7 @@
         <v>14</v>
       </c>
       <c r="H128" s="6">
-        <v>91</v>
+        <v>20</v>
       </c>
     </row>
     <row r="129" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5409,7 +5409,7 @@
         <v>14</v>
       </c>
       <c r="H129" s="8">
-        <v>71</v>
+        <v>17</v>
       </c>
     </row>
     <row r="130" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5435,7 +5435,7 @@
         <v>14</v>
       </c>
       <c r="H130" s="6">
-        <v>102</v>
+        <v>27</v>
       </c>
     </row>
     <row r="131" ht="22" customHeight="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5461,7 +5461,7 @@
         <v>14</v>
       </c>
       <c r="H131" s="8">
-        <v>32</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>
